--- a/test_case/AcuRev4100/4100_test_case.xlsx
+++ b/test_case/AcuRev4100/4100_test_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\branch_lcs_20250206\autotest\test_case\AcuRev4100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B3933A-5A0E-48DE-86DA-04B895D26423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B55B11-D9B1-43C9-A464-7C3B2DE368FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="Input_Current_Angle" sheetId="8" r:id="rId10"/>
     <sheet name="Load_Nature" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="180">
   <si>
     <t>字符</t>
   </si>
@@ -439,55 +439,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Function_AcuRev4100_004_01_case1</t>
-  </si>
-  <si>
-    <t>Function_AcuRev4100_004_01_case2</t>
-  </si>
-  <si>
-    <t>Function_AcuRev4100_004_01_case3</t>
-  </si>
-  <si>
-    <t>Function_AcuRev4100_004_01_case4</t>
-  </si>
-  <si>
-    <t>Function_AcuRev4100_004_01_case5</t>
-  </si>
-  <si>
-    <t>Function_AcuRev4100_004_01_case10_3</t>
-  </si>
-  <si>
     <t>Function_AcuRev4100_004_01_case11</t>
   </si>
   <si>
     <t>Function_AcuRev4100_004_01_case13</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case6</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case7</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case8</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case9</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case10</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case10_1</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case10_2</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case10_4</t>
-  </si>
-  <si>
-    <t>Fault_AcuRev4100_004_01_case10_5</t>
   </si>
   <si>
     <t>Function_AcuRev4100_004_01_case12</t>
@@ -515,18 +470,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>True Reactive Power</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Function_AcuRev4100_004_01_case18</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Function_AcuRev4100_004_01_case21</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Function_AcuRev4100_004_02_case2</t>
   </si>
   <si>
@@ -616,6 +559,111 @@
   <si>
     <t>Fault_AcuRev4100_005_01_case7</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>test_case</t>
+  </si>
+  <si>
+    <t>Phase_A_Voltage</t>
+  </si>
+  <si>
+    <t>Phase_B_Voltage</t>
+  </si>
+  <si>
+    <t>Phase_C_Voltage</t>
+  </si>
+  <si>
+    <t>Phase_A_Current</t>
+  </si>
+  <si>
+    <t>Phase_B_Current</t>
+  </si>
+  <si>
+    <t>Phase_C_Current</t>
+  </si>
+  <si>
+    <t>Va_angle</t>
+  </si>
+  <si>
+    <t>Vb_angle</t>
+  </si>
+  <si>
+    <t>Vc_angle</t>
+  </si>
+  <si>
+    <t>Ia_angle</t>
+  </si>
+  <si>
+    <t>Ib_angle</t>
+  </si>
+  <si>
+    <t>Ic_angle</t>
+  </si>
+  <si>
+    <t>User_Channel</t>
+  </si>
+  <si>
+    <t>Reactive Power Calculation Method</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case1</t>
+  </si>
+  <si>
+    <t>user1</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case2</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case3</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case4</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case5</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case6</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case7</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case8</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case9</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case10</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case10_1</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case10_2</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case10_3</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case10_4</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_004_01_case10_5</t>
+  </si>
+  <si>
+    <t>user1,user2,user3</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case18</t>
+  </si>
+  <si>
+    <t>True Reactive Power</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case21</t>
   </si>
 </sst>
 </file>
@@ -719,12 +767,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -758,9 +809,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{4338F8C4-D469-4464-93F2-E6CEB331BC97}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1400,7 +1467,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1441,7 +1508,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -1482,7 +1549,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -1523,7 +1590,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -1564,7 +1631,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -1605,7 +1672,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -1646,7 +1713,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -3585,1153 +3652,1153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="11">
+        <v>69</v>
+      </c>
+      <c r="C2" s="11">
+        <v>69</v>
+      </c>
+      <c r="D2" s="11">
+        <v>69</v>
+      </c>
+      <c r="E2" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2" s="11">
+        <v>4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <v>240</v>
+      </c>
+      <c r="J2" s="11">
+        <v>120</v>
+      </c>
+      <c r="K2" s="11">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11">
+        <v>240</v>
+      </c>
+      <c r="M2" s="11">
+        <v>120</v>
+      </c>
+      <c r="N2" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="11">
+        <v>120</v>
+      </c>
+      <c r="C3" s="11">
+        <v>120</v>
+      </c>
+      <c r="D3" s="11">
+        <v>120</v>
+      </c>
+      <c r="E3" s="11">
+        <v>3</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>3</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <v>240</v>
+      </c>
+      <c r="J3" s="11">
+        <v>120</v>
+      </c>
+      <c r="K3" s="11">
+        <v>330</v>
+      </c>
+      <c r="L3" s="11">
+        <v>210</v>
+      </c>
+      <c r="M3" s="11">
+        <v>90</v>
+      </c>
+      <c r="N3" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="11">
+        <v>220</v>
+      </c>
+      <c r="C4" s="11">
+        <v>220</v>
+      </c>
+      <c r="D4" s="11">
+        <v>220</v>
+      </c>
+      <c r="E4" s="11">
+        <v>4</v>
+      </c>
+      <c r="F4" s="11">
+        <v>4</v>
+      </c>
+      <c r="G4" s="11">
+        <v>4</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <v>240</v>
+      </c>
+      <c r="J4" s="11">
+        <v>120</v>
+      </c>
+      <c r="K4" s="11">
+        <v>240</v>
+      </c>
+      <c r="L4" s="11">
+        <v>120</v>
+      </c>
+      <c r="M4" s="11">
+        <v>0</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="11">
+        <v>230</v>
+      </c>
+      <c r="C5" s="11">
+        <v>230</v>
+      </c>
+      <c r="D5" s="11">
+        <v>230</v>
+      </c>
+      <c r="E5" s="11">
+        <v>5</v>
+      </c>
+      <c r="F5" s="11">
+        <v>5</v>
+      </c>
+      <c r="G5" s="11">
+        <v>5</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <v>240</v>
+      </c>
+      <c r="J5" s="11">
+        <v>120</v>
+      </c>
+      <c r="K5" s="11">
+        <v>135</v>
+      </c>
+      <c r="L5" s="11">
+        <v>15</v>
+      </c>
+      <c r="M5" s="11">
+        <v>255</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="11">
+        <v>400</v>
+      </c>
+      <c r="C6" s="11">
+        <v>400</v>
+      </c>
+      <c r="D6" s="11">
+        <v>400</v>
+      </c>
+      <c r="E6" s="11">
+        <v>4</v>
+      </c>
+      <c r="F6" s="11">
+        <v>4</v>
+      </c>
+      <c r="G6" s="11">
+        <v>4</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <v>240</v>
+      </c>
+      <c r="J6" s="11">
+        <v>120</v>
+      </c>
+      <c r="K6" s="11">
+        <v>30</v>
+      </c>
+      <c r="L6" s="11">
+        <v>270</v>
+      </c>
+      <c r="M6" s="11">
+        <v>150</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="11">
+        <v>220</v>
+      </c>
+      <c r="C7" s="11">
+        <v>220</v>
+      </c>
+      <c r="D7" s="11">
+        <v>220</v>
+      </c>
+      <c r="E7" s="11">
+        <v>4</v>
+      </c>
+      <c r="F7" s="11">
+        <v>4</v>
+      </c>
+      <c r="G7" s="11">
+        <v>4</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11">
+        <v>240</v>
+      </c>
+      <c r="J7" s="11">
+        <v>120</v>
+      </c>
+      <c r="K7" s="11">
+        <v>270</v>
+      </c>
+      <c r="L7" s="11">
+        <v>150</v>
+      </c>
+      <c r="M7" s="11">
+        <v>30</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="11">
+        <v>220</v>
+      </c>
+      <c r="C8" s="11">
+        <v>220</v>
+      </c>
+      <c r="D8" s="11">
+        <v>220</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F8" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11">
+        <v>240</v>
+      </c>
+      <c r="J8" s="11">
+        <v>120</v>
+      </c>
+      <c r="K8" s="11">
+        <v>180</v>
+      </c>
+      <c r="L8" s="11">
+        <v>60</v>
+      </c>
+      <c r="M8" s="11">
+        <v>300</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" s="11">
+        <v>220</v>
+      </c>
+      <c r="C9" s="11">
+        <v>220</v>
+      </c>
+      <c r="D9" s="11">
+        <v>220</v>
+      </c>
+      <c r="E9" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="F9" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G9" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>240</v>
+      </c>
+      <c r="J9" s="11">
+        <v>120</v>
+      </c>
+      <c r="K9" s="11">
+        <v>90</v>
+      </c>
+      <c r="L9" s="11">
+        <v>330</v>
+      </c>
+      <c r="M9" s="11">
+        <v>210</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="11">
+        <v>69</v>
+      </c>
+      <c r="C10" s="11">
+        <v>69</v>
+      </c>
+      <c r="D10" s="11">
+        <v>69</v>
+      </c>
+      <c r="E10" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>240</v>
+      </c>
+      <c r="J10" s="11">
+        <v>120</v>
+      </c>
+      <c r="K10" s="11">
+        <v>330</v>
+      </c>
+      <c r="L10" s="11">
+        <v>210</v>
+      </c>
+      <c r="M10" s="11">
+        <v>90</v>
+      </c>
+      <c r="N10" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="11">
+        <v>220</v>
+      </c>
+      <c r="C11" s="11">
+        <v>220</v>
+      </c>
+      <c r="D11" s="11">
+        <v>220</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>240</v>
+      </c>
+      <c r="J11" s="11">
+        <v>120</v>
+      </c>
+      <c r="K11" s="11">
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
+        <v>240</v>
+      </c>
+      <c r="M11" s="11">
+        <v>120</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="11">
+        <v>220</v>
+      </c>
+      <c r="C12" s="11">
+        <v>220</v>
+      </c>
+      <c r="D12" s="11">
+        <v>220</v>
+      </c>
+      <c r="E12" s="14">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>240</v>
+      </c>
+      <c r="J12" s="11">
+        <v>120</v>
+      </c>
+      <c r="K12" s="11">
+        <v>0</v>
+      </c>
+      <c r="L12" s="11">
+        <v>240</v>
+      </c>
+      <c r="M12" s="11">
+        <v>120</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="11">
+        <v>220</v>
+      </c>
+      <c r="C13" s="11">
+        <v>220</v>
+      </c>
+      <c r="D13" s="11">
+        <v>220</v>
+      </c>
+      <c r="E13" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="F13" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G13" s="15">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11">
+        <v>240</v>
+      </c>
+      <c r="J13" s="11">
+        <v>120</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0</v>
+      </c>
+      <c r="L13" s="11">
+        <v>240</v>
+      </c>
+      <c r="M13" s="11">
+        <v>120</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="11">
+        <v>220</v>
+      </c>
+      <c r="C14" s="11">
+        <v>220</v>
+      </c>
+      <c r="D14" s="11">
+        <v>220</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11">
+        <v>240</v>
+      </c>
+      <c r="J14" s="11">
+        <v>120</v>
+      </c>
+      <c r="K14" s="11">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11">
+        <v>240</v>
+      </c>
+      <c r="M14" s="11">
+        <v>120</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15" s="14">
+        <v>68</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>10</v>
+      </c>
+      <c r="E15" s="11">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11">
+        <v>1</v>
+      </c>
+      <c r="G15" s="11">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11">
+        <v>240</v>
+      </c>
+      <c r="J15" s="11">
+        <v>120</v>
+      </c>
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
+        <v>240</v>
+      </c>
+      <c r="M15" s="11">
+        <v>120</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="15">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="C16" s="15">
+        <v>9</v>
+      </c>
+      <c r="D16" s="15">
+        <v>9</v>
+      </c>
+      <c r="E16" s="11">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11">
+        <v>1</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <v>240</v>
+      </c>
+      <c r="J16" s="11">
+        <v>120</v>
+      </c>
+      <c r="K16" s="11">
+        <v>0</v>
+      </c>
+      <c r="L16" s="11">
+        <v>240</v>
+      </c>
+      <c r="M16" s="11">
+        <v>120</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="11">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11">
+        <v>120</v>
+      </c>
+      <c r="D17" s="11">
+        <v>120</v>
+      </c>
+      <c r="E17" s="11">
+        <v>3</v>
+      </c>
+      <c r="F17" s="11">
+        <v>4</v>
+      </c>
+      <c r="G17" s="11">
+        <v>5</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
+        <v>240</v>
+      </c>
+      <c r="J17" s="11">
+        <v>120</v>
+      </c>
+      <c r="K17" s="11">
+        <v>0</v>
+      </c>
+      <c r="L17" s="11">
+        <v>240</v>
+      </c>
+      <c r="M17" s="11">
+        <v>120</v>
+      </c>
+      <c r="N17" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="11">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11">
+        <v>69</v>
+      </c>
+      <c r="D18" s="11">
+        <v>69</v>
+      </c>
+      <c r="E18" s="11">
+        <v>3</v>
+      </c>
+      <c r="F18" s="11">
+        <v>3</v>
+      </c>
+      <c r="G18" s="11">
+        <v>3</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0</v>
+      </c>
+      <c r="I18" s="11">
+        <v>240</v>
+      </c>
+      <c r="J18" s="11">
+        <v>120</v>
+      </c>
+      <c r="K18" s="11">
+        <v>330</v>
+      </c>
+      <c r="L18" s="11">
+        <v>210</v>
+      </c>
+      <c r="M18" s="11">
+        <v>90</v>
+      </c>
+      <c r="N18" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="11">
+        <v>220</v>
+      </c>
+      <c r="C19" s="11">
+        <v>220</v>
+      </c>
+      <c r="D19" s="11">
+        <v>220</v>
+      </c>
+      <c r="E19" s="11">
+        <v>4</v>
+      </c>
+      <c r="F19" s="11">
+        <v>4</v>
+      </c>
+      <c r="G19" s="11">
+        <v>4</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
+        <v>240</v>
+      </c>
+      <c r="J19" s="11">
+        <v>120</v>
+      </c>
+      <c r="K19" s="11">
+        <v>240</v>
+      </c>
+      <c r="L19" s="11">
+        <v>120</v>
+      </c>
+      <c r="M19" s="11">
+        <v>0</v>
+      </c>
+      <c r="N19" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="11">
+        <v>230</v>
+      </c>
+      <c r="C20" s="11">
+        <v>230</v>
+      </c>
+      <c r="D20" s="11">
+        <v>230</v>
+      </c>
+      <c r="E20" s="11">
+        <v>5</v>
+      </c>
+      <c r="F20" s="11">
+        <v>5</v>
+      </c>
+      <c r="G20" s="11">
+        <v>5</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11">
+        <v>240</v>
+      </c>
+      <c r="J20" s="11">
+        <v>120</v>
+      </c>
+      <c r="K20" s="11">
+        <v>135</v>
+      </c>
+      <c r="L20" s="11">
+        <v>15</v>
+      </c>
+      <c r="M20" s="11">
+        <v>255</v>
+      </c>
+      <c r="N20" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="11">
+        <v>400</v>
+      </c>
+      <c r="C21" s="11">
+        <v>400</v>
+      </c>
+      <c r="D21" s="11">
+        <v>400</v>
+      </c>
+      <c r="E21" s="11">
+        <v>5</v>
+      </c>
+      <c r="F21" s="11">
+        <v>5</v>
+      </c>
+      <c r="G21" s="11">
+        <v>5</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <v>240</v>
+      </c>
+      <c r="J21" s="11">
+        <v>120</v>
+      </c>
+      <c r="K21" s="11">
         <v>30</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2">
-        <v>69</v>
-      </c>
-      <c r="C2">
-        <v>69</v>
-      </c>
-      <c r="D2">
-        <v>69</v>
-      </c>
-      <c r="E2">
+      <c r="L21" s="11">
+        <v>270</v>
+      </c>
+      <c r="M21" s="11">
+        <v>150</v>
+      </c>
+      <c r="N21" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="11">
+        <v>120</v>
+      </c>
+      <c r="C22" s="11">
+        <v>120</v>
+      </c>
+      <c r="D22" s="11">
+        <v>120</v>
+      </c>
+      <c r="E22" s="11">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="F22" s="11">
         <v>4</v>
       </c>
-      <c r="G2">
+      <c r="G22" s="11">
         <v>5</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>240</v>
-      </c>
-      <c r="J2">
-        <v>120</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>240</v>
-      </c>
-      <c r="M2">
-        <v>120</v>
-      </c>
-      <c r="N2">
+      <c r="H22" s="11">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <v>240</v>
+      </c>
+      <c r="J22" s="11">
+        <v>120</v>
+      </c>
+      <c r="K22" s="11">
+        <v>0</v>
+      </c>
+      <c r="L22" s="11">
+        <v>240</v>
+      </c>
+      <c r="M22" s="11">
+        <v>120</v>
+      </c>
+      <c r="N22" s="11">
         <v>0.2</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3">
-        <v>120</v>
-      </c>
-      <c r="C3">
-        <v>120</v>
-      </c>
-      <c r="D3">
-        <v>120</v>
-      </c>
-      <c r="E3">
+      <c r="O22" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B23" s="11">
+        <v>120</v>
+      </c>
+      <c r="C23" s="11">
+        <v>120</v>
+      </c>
+      <c r="D23" s="11">
+        <v>120</v>
+      </c>
+      <c r="E23" s="11">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>240</v>
-      </c>
-      <c r="J3">
-        <v>120</v>
-      </c>
-      <c r="K3">
+      <c r="F23" s="11">
+        <v>4</v>
+      </c>
+      <c r="G23" s="11">
+        <v>5</v>
+      </c>
+      <c r="H23" s="11">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
+        <v>240</v>
+      </c>
+      <c r="J23" s="11">
+        <v>120</v>
+      </c>
+      <c r="K23" s="11">
         <v>330</v>
       </c>
-      <c r="L3">
+      <c r="L23" s="11">
         <v>210</v>
       </c>
-      <c r="M3">
+      <c r="M23" s="11">
         <v>90</v>
       </c>
-      <c r="N3">
+      <c r="N23" s="11">
         <v>0.2</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4">
-        <v>220</v>
-      </c>
-      <c r="C4">
-        <v>220</v>
-      </c>
-      <c r="D4">
-        <v>220</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>240</v>
-      </c>
-      <c r="J4">
-        <v>120</v>
-      </c>
-      <c r="K4">
-        <v>240</v>
-      </c>
-      <c r="L4">
-        <v>120</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0.2</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5">
-        <v>230</v>
-      </c>
-      <c r="C5">
-        <v>230</v>
-      </c>
-      <c r="D5">
-        <v>230</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>240</v>
-      </c>
-      <c r="J5">
-        <v>120</v>
-      </c>
-      <c r="K5">
-        <v>135</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
-      </c>
-      <c r="M5">
-        <v>255</v>
-      </c>
-      <c r="N5">
-        <v>0.2</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6">
-        <v>400</v>
-      </c>
-      <c r="C6">
-        <v>400</v>
-      </c>
-      <c r="D6">
-        <v>400</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>240</v>
-      </c>
-      <c r="J6">
-        <v>120</v>
-      </c>
-      <c r="K6">
-        <v>30</v>
-      </c>
-      <c r="L6">
-        <v>270</v>
-      </c>
-      <c r="M6">
-        <v>150</v>
-      </c>
-      <c r="N6">
-        <v>0.2</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7">
-        <v>220</v>
-      </c>
-      <c r="C7">
-        <v>220</v>
-      </c>
-      <c r="D7">
-        <v>220</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>240</v>
-      </c>
-      <c r="J7">
-        <v>120</v>
-      </c>
-      <c r="K7">
-        <v>270</v>
-      </c>
-      <c r="L7">
-        <v>150</v>
-      </c>
-      <c r="M7">
-        <v>30</v>
-      </c>
-      <c r="N7">
-        <v>0.2</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8">
-        <v>220</v>
-      </c>
-      <c r="C8">
-        <v>220</v>
-      </c>
-      <c r="D8">
-        <v>220</v>
-      </c>
-      <c r="E8">
-        <v>3.5</v>
-      </c>
-      <c r="F8">
-        <v>3.5</v>
-      </c>
-      <c r="G8">
-        <v>3.5</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>240</v>
-      </c>
-      <c r="J8">
-        <v>120</v>
-      </c>
-      <c r="K8">
-        <v>180</v>
-      </c>
-      <c r="L8">
-        <v>60</v>
-      </c>
-      <c r="M8">
-        <v>300</v>
-      </c>
-      <c r="N8">
-        <v>0.2</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9">
-        <v>220</v>
-      </c>
-      <c r="C9">
-        <v>220</v>
-      </c>
-      <c r="D9">
-        <v>220</v>
-      </c>
-      <c r="E9">
-        <v>4.5</v>
-      </c>
-      <c r="F9">
-        <v>4.5</v>
-      </c>
-      <c r="G9">
-        <v>4.5</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>240</v>
-      </c>
-      <c r="J9">
-        <v>120</v>
-      </c>
-      <c r="K9">
-        <v>90</v>
-      </c>
-      <c r="L9">
-        <v>330</v>
-      </c>
-      <c r="M9">
-        <v>210</v>
-      </c>
-      <c r="N9">
-        <v>0.2</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10">
-        <v>69</v>
-      </c>
-      <c r="C10">
-        <v>69</v>
-      </c>
-      <c r="D10">
-        <v>69</v>
-      </c>
-      <c r="E10">
-        <v>2.5</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>0.3</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>240</v>
-      </c>
-      <c r="J10">
-        <v>120</v>
-      </c>
-      <c r="K10">
-        <v>330</v>
-      </c>
-      <c r="L10">
-        <v>210</v>
-      </c>
-      <c r="M10">
-        <v>90</v>
-      </c>
-      <c r="N10">
-        <v>0.2</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11">
-        <v>220</v>
-      </c>
-      <c r="C11">
-        <v>220</v>
-      </c>
-      <c r="D11">
-        <v>220</v>
-      </c>
-      <c r="E11">
-        <v>0.05</v>
-      </c>
-      <c r="F11">
-        <v>0.2</v>
-      </c>
-      <c r="G11">
-        <v>0.25</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>240</v>
-      </c>
-      <c r="J11">
-        <v>120</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>240</v>
-      </c>
-      <c r="M11">
-        <v>120</v>
-      </c>
-      <c r="N11">
-        <v>0.2</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12">
-        <v>220</v>
-      </c>
-      <c r="C12">
-        <v>220</v>
-      </c>
-      <c r="D12">
-        <v>220</v>
-      </c>
-      <c r="E12" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F12" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="G12" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>240</v>
-      </c>
-      <c r="J12">
-        <v>120</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>240</v>
-      </c>
-      <c r="M12">
-        <v>120</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13">
-        <v>220</v>
-      </c>
-      <c r="C13">
-        <v>220</v>
-      </c>
-      <c r="D13">
-        <v>220</v>
-      </c>
-      <c r="E13" s="10">
-        <v>2E-3</v>
-      </c>
-      <c r="F13" s="10">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G13" s="10">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>240</v>
-      </c>
-      <c r="J13">
-        <v>120</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>240</v>
-      </c>
-      <c r="M13">
-        <v>120</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14">
-        <v>220</v>
-      </c>
-      <c r="C14">
-        <v>220</v>
-      </c>
-      <c r="D14">
-        <v>220</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0</v>
-      </c>
-      <c r="F14" s="10">
-        <v>0</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>240</v>
-      </c>
-      <c r="J14">
-        <v>120</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>240</v>
-      </c>
-      <c r="M14">
-        <v>120</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="9">
-        <v>68</v>
-      </c>
-      <c r="C15" s="9">
-        <v>30</v>
-      </c>
-      <c r="D15" s="9">
-        <v>10</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>240</v>
-      </c>
-      <c r="J15">
-        <v>120</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>240</v>
-      </c>
-      <c r="M15">
-        <v>120</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B16" s="10">
-        <v>9</v>
-      </c>
-      <c r="C16" s="10">
-        <v>9</v>
-      </c>
-      <c r="D16" s="10">
-        <v>9</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>240</v>
-      </c>
-      <c r="J16">
-        <v>120</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>240</v>
-      </c>
-      <c r="M16">
-        <v>120</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17">
-        <v>120</v>
-      </c>
-      <c r="C17">
-        <v>120</v>
-      </c>
-      <c r="D17">
-        <v>120</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>240</v>
-      </c>
-      <c r="J17">
-        <v>120</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>240</v>
-      </c>
-      <c r="M17">
-        <v>120</v>
-      </c>
-      <c r="N17">
-        <v>0.2</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18">
-        <v>69</v>
-      </c>
-      <c r="C18">
-        <v>69</v>
-      </c>
-      <c r="D18">
-        <v>69</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>240</v>
-      </c>
-      <c r="J18">
-        <v>120</v>
-      </c>
-      <c r="K18">
-        <v>330</v>
-      </c>
-      <c r="L18">
-        <v>210</v>
-      </c>
-      <c r="M18">
-        <v>90</v>
-      </c>
-      <c r="N18">
-        <v>0.2</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19">
-        <v>220</v>
-      </c>
-      <c r="C19">
-        <v>220</v>
-      </c>
-      <c r="D19">
-        <v>220</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>4</v>
-      </c>
-      <c r="G19">
-        <v>4</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>240</v>
-      </c>
-      <c r="J19">
-        <v>120</v>
-      </c>
-      <c r="K19">
-        <v>240</v>
-      </c>
-      <c r="L19">
-        <v>120</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0.2</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20">
-        <v>230</v>
-      </c>
-      <c r="C20">
-        <v>230</v>
-      </c>
-      <c r="D20">
-        <v>230</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>240</v>
-      </c>
-      <c r="J20">
-        <v>120</v>
-      </c>
-      <c r="K20">
-        <v>135</v>
-      </c>
-      <c r="L20">
-        <v>15</v>
-      </c>
-      <c r="M20">
-        <v>255</v>
-      </c>
-      <c r="N20">
-        <v>0.2</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B21">
-        <v>400</v>
-      </c>
-      <c r="C21">
-        <v>400</v>
-      </c>
-      <c r="D21">
-        <v>400</v>
-      </c>
-      <c r="E21">
-        <v>5</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>240</v>
-      </c>
-      <c r="J21">
-        <v>120</v>
-      </c>
-      <c r="K21">
-        <v>30</v>
-      </c>
-      <c r="L21">
-        <v>270</v>
-      </c>
-      <c r="M21">
-        <v>150</v>
-      </c>
-      <c r="N21">
-        <v>0.2</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B22">
-        <v>120</v>
-      </c>
-      <c r="C22">
-        <v>120</v>
-      </c>
-      <c r="D22">
-        <v>120</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22">
-        <v>4</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>240</v>
-      </c>
-      <c r="J22">
-        <v>120</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>240</v>
-      </c>
-      <c r="M22">
-        <v>120</v>
-      </c>
-      <c r="N22">
-        <v>0.2</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23">
-        <v>120</v>
-      </c>
-      <c r="C23">
-        <v>120</v>
-      </c>
-      <c r="D23">
-        <v>120</v>
-      </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
-      <c r="F23">
-        <v>4</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>240</v>
-      </c>
-      <c r="J23">
-        <v>120</v>
-      </c>
-      <c r="K23">
-        <v>330</v>
-      </c>
-      <c r="L23">
-        <v>210</v>
-      </c>
-      <c r="M23">
-        <v>90</v>
-      </c>
-      <c r="N23">
-        <v>0.2</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>132</v>
+      <c r="O23" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4801,15 +4868,15 @@
         <v>8</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B2">
         <v>69</v>
@@ -4851,7 +4918,7 @@
         <v>0.2</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P2" s="8" t="s">
         <v>74</v>
@@ -4859,7 +4926,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B3">
         <v>220</v>
@@ -4901,7 +4968,7 @@
         <v>0.2</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>74</v>
@@ -4909,7 +4976,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B4">
         <v>120</v>
@@ -4951,7 +5018,7 @@
         <v>0.2</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P4" s="8" t="s">
         <v>74</v>
@@ -4959,7 +5026,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B5">
         <v>220</v>
@@ -5001,7 +5068,7 @@
         <v>0.2</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P5" s="8" t="s">
         <v>74</v>
@@ -5009,7 +5076,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B6">
         <v>230</v>
@@ -5051,7 +5118,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P6" s="8" t="s">
         <v>74</v>
@@ -5059,7 +5126,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B7">
         <v>400</v>
@@ -5101,7 +5168,7 @@
         <v>0.2</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P7" s="8" t="s">
         <v>74</v>
@@ -5109,7 +5176,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>220</v>
@@ -5151,7 +5218,7 @@
         <v>0.2</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P8" s="8" t="s">
         <v>74</v>
@@ -5159,7 +5226,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="B9">
         <v>220</v>
@@ -5201,7 +5268,7 @@
         <v>0.2</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P9" s="8" t="s">
         <v>74</v>
@@ -5209,7 +5276,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B10">
         <v>220</v>
@@ -5251,7 +5318,7 @@
         <v>0.2</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P10" s="8" t="s">
         <v>74</v>
@@ -5259,7 +5326,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B11">
         <v>120</v>
@@ -5301,7 +5368,7 @@
         <v>0.2</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P11" s="8" t="s">
         <v>74</v>
@@ -5309,7 +5376,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B12">
         <v>220</v>
@@ -5351,7 +5418,7 @@
         <v>0.2</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P12" s="8" t="s">
         <v>74</v>
@@ -5359,7 +5426,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B13">
         <v>220</v>
@@ -5401,7 +5468,7 @@
         <v>74</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>74</v>
@@ -5409,7 +5476,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B14">
         <v>220</v>
@@ -5451,7 +5518,7 @@
         <v>74</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>74</v>
@@ -5459,7 +5526,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B15">
         <v>220</v>
@@ -5501,7 +5568,7 @@
         <v>74</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>74</v>
@@ -5509,7 +5576,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B16" s="9">
         <v>68</v>
@@ -5551,7 +5618,7 @@
         <v>74</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P16" s="8" t="s">
         <v>74</v>
@@ -5559,7 +5626,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B17" s="10">
         <v>9</v>
@@ -5601,7 +5668,7 @@
         <v>74</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="P17" s="8" t="s">
         <v>74</v>
@@ -5609,7 +5676,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B18">
         <v>120</v>
@@ -5651,7 +5718,7 @@
         <v>0.2</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>74</v>
@@ -5659,7 +5726,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="B19">
         <v>69</v>
@@ -5701,7 +5768,7 @@
         <v>0.2</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="P19" s="8" t="s">
         <v>74</v>
@@ -5709,7 +5776,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B20">
         <v>220</v>
@@ -5751,7 +5818,7 @@
         <v>0.2</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="P20" s="8" t="s">
         <v>74</v>
@@ -5759,7 +5826,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B21">
         <v>230</v>
@@ -5801,7 +5868,7 @@
         <v>0.2</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="P21" s="8" t="s">
         <v>74</v>
@@ -5809,7 +5876,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B22">
         <v>400</v>
@@ -5851,7 +5918,7 @@
         <v>0.2</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="P22" s="8" t="s">
         <v>74</v>

--- a/test_case/AcuRev4100/4100_test_case.xlsx
+++ b/test_case/AcuRev4100/4100_test_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\branch_lcs_20250206\autotest\test_case\AcuRev4100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B55B11-D9B1-43C9-A464-7C3B2DE368FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997CDC84-63EA-4B7E-8D7E-83D6739FD0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="3" r:id="rId1"/>
@@ -24,6 +24,9 @@
     <sheet name="Phase_Voltage_Angle" sheetId="7" r:id="rId9"/>
     <sheet name="Input_Current_Angle" sheetId="8" r:id="rId10"/>
     <sheet name="Load_Nature" sheetId="11" r:id="rId11"/>
+    <sheet name="Sequence_Component" sheetId="14" r:id="rId12"/>
+    <sheet name="Energy_5A_333mV_CT" sheetId="12" r:id="rId13"/>
+    <sheet name="Energy_20A_100mA_CT" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="264">
   <si>
     <t>字符</t>
   </si>
@@ -664,13 +667,323 @@
   </si>
   <si>
     <t>Function_AcuRev4100_004_01_case21</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_01_case8</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_01_case9</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_01_case10</t>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_005_01_case11</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_01_case12</t>
+  </si>
+  <si>
+    <t>一种负载类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_02_case1</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_02_case2</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_02_case3</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_005_02_case4</t>
+  </si>
+  <si>
+    <t>Load_Nature</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多种负载类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1E1p2w</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>接线类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>接线方式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2E3p3w</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_003_02_case7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3E3p4w</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_003_02_case8</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_003_02_case9</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_003_02_case18</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_003_02_case19</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_003_02_case20</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_003_02_case21</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待时间(min)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case3</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case3_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_010_01_case4_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_010_01_case4_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_010_01_case4_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_010_01_case6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>精度要求</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_010_01_case6_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_010_01_case6_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_010_01_case6_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case9</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case9_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_01_case11</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_02_case2</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_02_case3</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_02_case5</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_02_case6</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_01_case2_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_004_02_case2_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case3_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case3_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case3_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_009_01_case3_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fault_AcuRev4100_009_01_case3_5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case9</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case13_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_009_01_case13_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A_amplitude</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_amplitude</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_amplitude</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A_angle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_angle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_angle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>精度%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VUF</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUF</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待时间(min)</t>
+  </si>
+  <si>
+    <t>接线方式</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_02_case1</t>
+  </si>
+  <si>
+    <t>3E3p4w</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_02_case3_1</t>
+  </si>
+  <si>
+    <t>Function_AcuRev4100_010_02_case4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,6 +1028,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -775,7 +1096,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -812,16 +1133,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1415,16 +1745,18 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67CBA65C-FFBA-4D16-8B74-254EB1AB8DF0}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.6640625" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
@@ -1464,8 +1796,14 @@
       <c r="M1" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>139</v>
       </c>
@@ -1505,8 +1843,14 @@
       <c r="M2">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>138</v>
       </c>
@@ -1546,8 +1890,14 @@
       <c r="M3">
         <v>300</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>141</v>
       </c>
@@ -1587,8 +1937,14 @@
       <c r="M4">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>140</v>
       </c>
@@ -1628,8 +1984,14 @@
       <c r="M5">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>142</v>
       </c>
@@ -1669,8 +2031,14 @@
       <c r="M6">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>143</v>
       </c>
@@ -1710,8 +2078,14 @@
       <c r="M7">
         <v>270</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>144</v>
       </c>
@@ -1750,6 +2124,2439 @@
       </c>
       <c r="M8">
         <v>240</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>240</v>
+      </c>
+      <c r="J9">
+        <v>120</v>
+      </c>
+      <c r="K9">
+        <v>240</v>
+      </c>
+      <c r="L9">
+        <v>120</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>240</v>
+      </c>
+      <c r="J10">
+        <v>120</v>
+      </c>
+      <c r="K10">
+        <v>210</v>
+      </c>
+      <c r="L10">
+        <v>90</v>
+      </c>
+      <c r="M10">
+        <v>330</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>240</v>
+      </c>
+      <c r="J11">
+        <v>120</v>
+      </c>
+      <c r="K11">
+        <v>60</v>
+      </c>
+      <c r="L11">
+        <v>300</v>
+      </c>
+      <c r="M11">
+        <v>180</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>240</v>
+      </c>
+      <c r="J12">
+        <v>120</v>
+      </c>
+      <c r="K12">
+        <v>90</v>
+      </c>
+      <c r="L12">
+        <v>330</v>
+      </c>
+      <c r="M12">
+        <v>210</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>240</v>
+      </c>
+      <c r="J13">
+        <v>120</v>
+      </c>
+      <c r="K13">
+        <v>30</v>
+      </c>
+      <c r="L13">
+        <v>270</v>
+      </c>
+      <c r="M13">
+        <v>150</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>240</v>
+      </c>
+      <c r="J14">
+        <v>120</v>
+      </c>
+      <c r="K14">
+        <v>330</v>
+      </c>
+      <c r="L14">
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <v>120</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>240</v>
+      </c>
+      <c r="J15">
+        <v>120</v>
+      </c>
+      <c r="K15">
+        <v>330</v>
+      </c>
+      <c r="L15">
+        <v>30</v>
+      </c>
+      <c r="M15">
+        <v>90</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>240</v>
+      </c>
+      <c r="J16">
+        <v>120</v>
+      </c>
+      <c r="K16">
+        <v>330</v>
+      </c>
+      <c r="L16">
+        <v>30</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17">
+        <v>100</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>240</v>
+      </c>
+      <c r="J17">
+        <v>120</v>
+      </c>
+      <c r="K17">
+        <v>330</v>
+      </c>
+      <c r="L17">
+        <v>30</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D720F61-3218-4A02-B7D8-CDC001F03935}">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2">
+        <v>220</v>
+      </c>
+      <c r="C2">
+        <v>230</v>
+      </c>
+      <c r="D2">
+        <v>225</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>240</v>
+      </c>
+      <c r="G2">
+        <v>120</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="C3">
+        <v>220</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>240</v>
+      </c>
+      <c r="G3">
+        <v>120</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4">
+        <v>230</v>
+      </c>
+      <c r="C4">
+        <v>230</v>
+      </c>
+      <c r="D4">
+        <v>230</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>120</v>
+      </c>
+      <c r="G4">
+        <v>240</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>220</v>
+      </c>
+      <c r="D5">
+        <v>220</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>120</v>
+      </c>
+      <c r="G5">
+        <v>240</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>220</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>240</v>
+      </c>
+      <c r="G6">
+        <v>120</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>120</v>
+      </c>
+      <c r="G7">
+        <v>240</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="B8">
+        <v>220</v>
+      </c>
+      <c r="C8">
+        <v>220</v>
+      </c>
+      <c r="D8">
+        <v>220</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>240</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9">
+        <v>220</v>
+      </c>
+      <c r="C9">
+        <v>220</v>
+      </c>
+      <c r="D9">
+        <v>200</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10">
+        <v>220</v>
+      </c>
+      <c r="C10">
+        <v>220</v>
+      </c>
+      <c r="D10">
+        <v>220</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>120</v>
+      </c>
+      <c r="G10">
+        <v>240</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>200</v>
+      </c>
+      <c r="D11">
+        <v>300</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>120</v>
+      </c>
+      <c r="G11">
+        <v>120</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>240</v>
+      </c>
+      <c r="G12">
+        <v>120</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>120</v>
+      </c>
+      <c r="G13">
+        <v>240</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>240</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>240</v>
+      </c>
+      <c r="G16">
+        <v>120</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <v>60</v>
+      </c>
+      <c r="F17">
+        <v>240</v>
+      </c>
+      <c r="G17">
+        <v>120</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18">
+        <v>220</v>
+      </c>
+      <c r="C18">
+        <v>220</v>
+      </c>
+      <c r="D18">
+        <v>220</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>240</v>
+      </c>
+      <c r="G18">
+        <v>120</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19">
+        <v>220</v>
+      </c>
+      <c r="C19">
+        <v>220</v>
+      </c>
+      <c r="D19">
+        <v>220</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>120</v>
+      </c>
+      <c r="G19">
+        <v>240</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A436D8E1-A32A-4B63-AF96-6782A5B18BBD}">
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2">
+        <v>120</v>
+      </c>
+      <c r="C2">
+        <v>120</v>
+      </c>
+      <c r="D2">
+        <v>120</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>240</v>
+      </c>
+      <c r="J2">
+        <v>120</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>240</v>
+      </c>
+      <c r="M2">
+        <v>120</v>
+      </c>
+      <c r="N2">
+        <v>10</v>
+      </c>
+      <c r="O2">
+        <v>0.2</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3">
+        <v>69</v>
+      </c>
+      <c r="C3">
+        <v>69</v>
+      </c>
+      <c r="D3">
+        <v>69</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>240</v>
+      </c>
+      <c r="J3">
+        <v>120</v>
+      </c>
+      <c r="K3">
+        <v>330</v>
+      </c>
+      <c r="L3">
+        <v>210</v>
+      </c>
+      <c r="M3">
+        <v>90</v>
+      </c>
+      <c r="N3">
+        <v>10</v>
+      </c>
+      <c r="O3">
+        <v>0.2</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4">
+        <v>220</v>
+      </c>
+      <c r="C4">
+        <v>220</v>
+      </c>
+      <c r="D4">
+        <v>220</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>240</v>
+      </c>
+      <c r="J4">
+        <v>120</v>
+      </c>
+      <c r="K4">
+        <v>240</v>
+      </c>
+      <c r="L4">
+        <v>120</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4">
+        <v>0.2</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5">
+        <v>220</v>
+      </c>
+      <c r="C5">
+        <v>220</v>
+      </c>
+      <c r="D5">
+        <v>220</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>240</v>
+      </c>
+      <c r="J5">
+        <v>120</v>
+      </c>
+      <c r="K5">
+        <v>150</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>270</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>0.2</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6">
+        <v>400</v>
+      </c>
+      <c r="C6">
+        <v>400</v>
+      </c>
+      <c r="D6">
+        <v>400</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>240</v>
+      </c>
+      <c r="J6">
+        <v>120</v>
+      </c>
+      <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>270</v>
+      </c>
+      <c r="M6">
+        <v>150</v>
+      </c>
+      <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7">
+        <v>120</v>
+      </c>
+      <c r="C7">
+        <v>120</v>
+      </c>
+      <c r="D7">
+        <v>120</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>240</v>
+      </c>
+      <c r="J7">
+        <v>120</v>
+      </c>
+      <c r="K7">
+        <v>270</v>
+      </c>
+      <c r="L7">
+        <v>150</v>
+      </c>
+      <c r="M7">
+        <v>30</v>
+      </c>
+      <c r="N7">
+        <v>10</v>
+      </c>
+      <c r="O7">
+        <v>0.2</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8">
+        <v>120</v>
+      </c>
+      <c r="C8">
+        <v>120</v>
+      </c>
+      <c r="D8">
+        <v>120</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>240</v>
+      </c>
+      <c r="J8">
+        <v>120</v>
+      </c>
+      <c r="K8">
+        <v>180</v>
+      </c>
+      <c r="L8">
+        <v>60</v>
+      </c>
+      <c r="M8">
+        <v>300</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>0.2</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9">
+        <v>120</v>
+      </c>
+      <c r="C9">
+        <v>120</v>
+      </c>
+      <c r="D9">
+        <v>120</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>240</v>
+      </c>
+      <c r="J9">
+        <v>120</v>
+      </c>
+      <c r="K9">
+        <v>90</v>
+      </c>
+      <c r="L9">
+        <v>330</v>
+      </c>
+      <c r="M9">
+        <v>210</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9">
+        <v>0.2</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10">
+        <v>120</v>
+      </c>
+      <c r="C10">
+        <v>120</v>
+      </c>
+      <c r="D10">
+        <v>120</v>
+      </c>
+      <c r="E10">
+        <v>2.5</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>0.3</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>240</v>
+      </c>
+      <c r="J10">
+        <v>120</v>
+      </c>
+      <c r="K10">
+        <v>330</v>
+      </c>
+      <c r="L10">
+        <v>210</v>
+      </c>
+      <c r="M10">
+        <v>90</v>
+      </c>
+      <c r="N10">
+        <v>10</v>
+      </c>
+      <c r="O10">
+        <v>0.2</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11">
+        <v>120</v>
+      </c>
+      <c r="C11">
+        <v>120</v>
+      </c>
+      <c r="D11">
+        <v>120</v>
+      </c>
+      <c r="E11">
+        <v>0.05</v>
+      </c>
+      <c r="F11">
+        <v>0.1</v>
+      </c>
+      <c r="G11">
+        <v>0.25</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>240</v>
+      </c>
+      <c r="J11">
+        <v>120</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>240</v>
+      </c>
+      <c r="M11">
+        <v>120</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>0.4</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12">
+        <v>120</v>
+      </c>
+      <c r="C12">
+        <v>120</v>
+      </c>
+      <c r="D12">
+        <v>120</v>
+      </c>
+      <c r="E12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F12">
+        <v>0.02</v>
+      </c>
+      <c r="G12">
+        <v>0.04</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>240</v>
+      </c>
+      <c r="J12">
+        <v>120</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>240</v>
+      </c>
+      <c r="M12">
+        <v>120</v>
+      </c>
+      <c r="N12">
+        <v>10</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13">
+        <v>120</v>
+      </c>
+      <c r="C13">
+        <v>120</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+      <c r="E13" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="F13" s="15">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G13" s="15">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>240</v>
+      </c>
+      <c r="J13">
+        <v>120</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>240</v>
+      </c>
+      <c r="M13">
+        <v>120</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B14">
+        <v>120</v>
+      </c>
+      <c r="C14">
+        <v>120</v>
+      </c>
+      <c r="D14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>240</v>
+      </c>
+      <c r="J14">
+        <v>120</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>240</v>
+      </c>
+      <c r="M14">
+        <v>120</v>
+      </c>
+      <c r="N14">
+        <v>10</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15">
+        <v>120</v>
+      </c>
+      <c r="C15">
+        <v>120</v>
+      </c>
+      <c r="D15">
+        <v>120</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>240</v>
+      </c>
+      <c r="J15">
+        <v>120</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>240</v>
+      </c>
+      <c r="M15">
+        <v>120</v>
+      </c>
+      <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <v>0.2</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16">
+        <v>69</v>
+      </c>
+      <c r="C16">
+        <v>69</v>
+      </c>
+      <c r="D16">
+        <v>69</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>240</v>
+      </c>
+      <c r="J16">
+        <v>120</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>240</v>
+      </c>
+      <c r="M16">
+        <v>120</v>
+      </c>
+      <c r="N16">
+        <v>10</v>
+      </c>
+      <c r="O16">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B17">
+        <v>220</v>
+      </c>
+      <c r="C17">
+        <v>220</v>
+      </c>
+      <c r="D17">
+        <v>220</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>240</v>
+      </c>
+      <c r="J17">
+        <v>120</v>
+      </c>
+      <c r="K17">
+        <v>240</v>
+      </c>
+      <c r="L17">
+        <v>120</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>10</v>
+      </c>
+      <c r="O17">
+        <v>0.2</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18">
+        <v>220</v>
+      </c>
+      <c r="C18">
+        <v>220</v>
+      </c>
+      <c r="D18">
+        <v>220</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>240</v>
+      </c>
+      <c r="J18">
+        <v>120</v>
+      </c>
+      <c r="K18">
+        <v>150</v>
+      </c>
+      <c r="L18">
+        <v>30</v>
+      </c>
+      <c r="M18">
+        <v>270</v>
+      </c>
+      <c r="N18">
+        <v>10</v>
+      </c>
+      <c r="O18">
+        <v>0.2</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B19">
+        <v>400</v>
+      </c>
+      <c r="C19">
+        <v>400</v>
+      </c>
+      <c r="D19">
+        <v>400</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>240</v>
+      </c>
+      <c r="J19">
+        <v>120</v>
+      </c>
+      <c r="K19">
+        <v>30</v>
+      </c>
+      <c r="L19">
+        <v>270</v>
+      </c>
+      <c r="M19">
+        <v>150</v>
+      </c>
+      <c r="N19">
+        <v>10</v>
+      </c>
+      <c r="O19">
+        <v>0.2</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20">
+        <v>220</v>
+      </c>
+      <c r="C20">
+        <v>220</v>
+      </c>
+      <c r="D20">
+        <v>220</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>240</v>
+      </c>
+      <c r="J20">
+        <v>120</v>
+      </c>
+      <c r="K20">
+        <v>330</v>
+      </c>
+      <c r="L20">
+        <v>210</v>
+      </c>
+      <c r="M20">
+        <v>90</v>
+      </c>
+      <c r="N20">
+        <v>10</v>
+      </c>
+      <c r="O20">
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA65D10D-9E4B-4B9D-93C7-F7018DA4E348}">
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="17" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="16">
+        <v>120</v>
+      </c>
+      <c r="C2" s="16">
+        <v>120</v>
+      </c>
+      <c r="D2" s="16">
+        <v>120</v>
+      </c>
+      <c r="E2" s="16">
+        <v>10</v>
+      </c>
+      <c r="F2" s="16">
+        <v>15</v>
+      </c>
+      <c r="G2" s="16">
+        <v>20</v>
+      </c>
+      <c r="H2" s="16">
+        <v>0</v>
+      </c>
+      <c r="I2" s="16">
+        <v>240</v>
+      </c>
+      <c r="J2" s="16">
+        <v>120</v>
+      </c>
+      <c r="K2" s="16">
+        <v>0</v>
+      </c>
+      <c r="L2" s="16">
+        <v>240</v>
+      </c>
+      <c r="M2" s="16">
+        <v>120</v>
+      </c>
+      <c r="N2" s="16">
+        <v>10</v>
+      </c>
+      <c r="O2" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="16">
+        <v>69</v>
+      </c>
+      <c r="C3" s="16">
+        <v>69</v>
+      </c>
+      <c r="D3" s="16">
+        <v>69</v>
+      </c>
+      <c r="E3" s="16">
+        <v>3</v>
+      </c>
+      <c r="F3" s="16">
+        <v>3</v>
+      </c>
+      <c r="G3" s="16">
+        <v>3</v>
+      </c>
+      <c r="H3" s="16">
+        <v>0</v>
+      </c>
+      <c r="I3" s="16">
+        <v>240</v>
+      </c>
+      <c r="J3" s="16">
+        <v>120</v>
+      </c>
+      <c r="K3" s="16">
+        <v>330</v>
+      </c>
+      <c r="L3" s="16">
+        <v>210</v>
+      </c>
+      <c r="M3" s="16">
+        <v>90</v>
+      </c>
+      <c r="N3" s="16">
+        <v>10</v>
+      </c>
+      <c r="O3" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="16">
+        <v>220</v>
+      </c>
+      <c r="C4" s="16">
+        <v>220</v>
+      </c>
+      <c r="D4" s="16">
+        <v>220</v>
+      </c>
+      <c r="E4" s="16">
+        <v>10</v>
+      </c>
+      <c r="F4" s="16">
+        <v>10</v>
+      </c>
+      <c r="G4" s="16">
+        <v>10</v>
+      </c>
+      <c r="H4" s="16">
+        <v>0</v>
+      </c>
+      <c r="I4" s="16">
+        <v>240</v>
+      </c>
+      <c r="J4" s="16">
+        <v>120</v>
+      </c>
+      <c r="K4" s="16">
+        <v>240</v>
+      </c>
+      <c r="L4" s="16">
+        <v>120</v>
+      </c>
+      <c r="M4" s="16">
+        <v>0</v>
+      </c>
+      <c r="N4" s="16">
+        <v>10</v>
+      </c>
+      <c r="O4" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="16">
+        <v>220</v>
+      </c>
+      <c r="C5" s="16">
+        <v>220</v>
+      </c>
+      <c r="D5" s="16">
+        <v>220</v>
+      </c>
+      <c r="E5" s="16">
+        <v>10</v>
+      </c>
+      <c r="F5" s="16">
+        <v>10</v>
+      </c>
+      <c r="G5" s="16">
+        <v>10</v>
+      </c>
+      <c r="H5" s="16">
+        <v>0</v>
+      </c>
+      <c r="I5" s="16">
+        <v>240</v>
+      </c>
+      <c r="J5" s="16">
+        <v>120</v>
+      </c>
+      <c r="K5" s="16">
+        <v>150</v>
+      </c>
+      <c r="L5" s="16">
+        <v>30</v>
+      </c>
+      <c r="M5" s="16">
+        <v>270</v>
+      </c>
+      <c r="N5" s="16">
+        <v>10</v>
+      </c>
+      <c r="O5" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="16">
+        <v>400</v>
+      </c>
+      <c r="C6" s="16">
+        <v>400</v>
+      </c>
+      <c r="D6" s="16">
+        <v>400</v>
+      </c>
+      <c r="E6" s="16">
+        <v>20</v>
+      </c>
+      <c r="F6" s="16">
+        <v>20</v>
+      </c>
+      <c r="G6" s="16">
+        <v>20</v>
+      </c>
+      <c r="H6" s="16">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16">
+        <v>240</v>
+      </c>
+      <c r="J6" s="16">
+        <v>120</v>
+      </c>
+      <c r="K6" s="16">
+        <v>30</v>
+      </c>
+      <c r="L6" s="16">
+        <v>270</v>
+      </c>
+      <c r="M6" s="16">
+        <v>150</v>
+      </c>
+      <c r="N6" s="16">
+        <v>10</v>
+      </c>
+      <c r="O6" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" s="16">
+        <v>120</v>
+      </c>
+      <c r="C7" s="16">
+        <v>120</v>
+      </c>
+      <c r="D7" s="16">
+        <v>120</v>
+      </c>
+      <c r="E7" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="16">
+        <v>2</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1</v>
+      </c>
+      <c r="H7" s="16">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16">
+        <v>240</v>
+      </c>
+      <c r="J7" s="16">
+        <v>120</v>
+      </c>
+      <c r="K7" s="16">
+        <v>330</v>
+      </c>
+      <c r="L7" s="16">
+        <v>210</v>
+      </c>
+      <c r="M7" s="16">
+        <v>90</v>
+      </c>
+      <c r="N7" s="16">
+        <v>10</v>
+      </c>
+      <c r="O7" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8" s="16">
+        <v>120</v>
+      </c>
+      <c r="C8" s="16">
+        <v>120</v>
+      </c>
+      <c r="D8" s="16">
+        <v>120</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.95</v>
+      </c>
+      <c r="H8" s="16">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16">
+        <v>240</v>
+      </c>
+      <c r="J8" s="16">
+        <v>120</v>
+      </c>
+      <c r="K8" s="16">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16">
+        <v>240</v>
+      </c>
+      <c r="M8" s="16">
+        <v>120</v>
+      </c>
+      <c r="N8" s="16">
+        <v>10</v>
+      </c>
+      <c r="O8" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -2840,7 +5647,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07D32AA-0210-4430-934B-FE9DE161B8E7}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.44140625" customWidth="1"/>
@@ -2850,7 +5657,7 @@
     <col min="6" max="6" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
@@ -2869,8 +5676,11 @@
       <c r="F1" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>48</v>
       </c>
@@ -2890,7 +5700,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>49</v>
       </c>
@@ -2910,7 +5720,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>50</v>
       </c>
@@ -2930,7 +5740,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
@@ -2950,7 +5760,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>52</v>
       </c>
@@ -2970,7 +5780,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
@@ -2990,7 +5800,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
@@ -3010,7 +5820,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>55</v>
       </c>
@@ -3030,7 +5840,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -3050,7 +5860,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>57</v>
       </c>
@@ -3070,7 +5880,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
@@ -3090,7 +5900,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
@@ -3110,7 +5920,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>95</v>
       </c>
@@ -3129,8 +5939,11 @@
       <c r="F14" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>96</v>
       </c>
@@ -3149,8 +5962,11 @@
       <c r="F15" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>97</v>
       </c>
@@ -3169,8 +5985,11 @@
       <c r="F16" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>98</v>
       </c>
@@ -3189,8 +6008,11 @@
       <c r="F17" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>99</v>
       </c>
@@ -3209,8 +6031,11 @@
       <c r="F18" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>100</v>
       </c>
@@ -3229,8 +6054,11 @@
       <c r="F19" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>101</v>
       </c>
@@ -3248,6 +6076,78 @@
       </c>
       <c r="F20" s="8" t="s">
         <v>94</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3258,7 +6158,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE00F74-D4A6-4CBF-98F0-64C4963325D6}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.44140625" customWidth="1"/>
@@ -3268,7 +6168,7 @@
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
@@ -3287,8 +6187,11 @@
       <c r="F1" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
@@ -3308,7 +6211,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,7 +6231,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>62</v>
       </c>
@@ -3348,7 +6251,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>63</v>
       </c>
@@ -3368,7 +6271,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>64</v>
       </c>
@@ -3388,7 +6291,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
@@ -3408,7 +6311,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>66</v>
       </c>
@@ -3428,7 +6331,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>67</v>
       </c>
@@ -3448,7 +6351,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>68</v>
       </c>
@@ -3468,7 +6371,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>69</v>
       </c>
@@ -3488,7 +6391,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>70</v>
       </c>
@@ -3508,7 +6411,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>102</v>
       </c>
@@ -3527,8 +6430,11 @@
       <c r="F13" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>103</v>
       </c>
@@ -3547,8 +6453,11 @@
       <c r="F14" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>104</v>
       </c>
@@ -3567,8 +6476,11 @@
       <c r="F15" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>105</v>
       </c>
@@ -3587,8 +6499,11 @@
       <c r="F16" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>106</v>
       </c>
@@ -3607,8 +6522,11 @@
       <c r="F17" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>107</v>
       </c>
@@ -3626,6 +6544,101 @@
       </c>
       <c r="F18" s="8" t="s">
         <v>94</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B20" s="1">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1">
+        <v>20</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" s="1">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B22" s="1">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3636,7 +6649,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD5C573-9E50-4AA9-8BD4-3B806E717AC2}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.6640625" customWidth="1"/>
@@ -3744,10 +6757,10 @@
       <c r="N2" s="11">
         <v>0.2</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3794,34 +6807,34 @@
       <c r="N3" s="11">
         <v>0.2</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="B4" s="11">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="C4" s="11">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="D4" s="11">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E4" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" s="11">
         <v>0</v>
@@ -3833,45 +6846,45 @@
         <v>120</v>
       </c>
       <c r="K4" s="11">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="L4" s="11">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="M4" s="11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N4" s="11">
         <v>0.2</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="11">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C5" s="11">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D5" s="11">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E5" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="11">
         <v>0</v>
@@ -3883,45 +6896,45 @@
         <v>120</v>
       </c>
       <c r="K5" s="11">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="L5" s="11">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="M5" s="11">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="N5" s="11">
         <v>0.2</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="11">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="C6" s="11">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="D6" s="11">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="E6" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="11">
         <v>0</v>
@@ -3933,36 +6946,36 @@
         <v>120</v>
       </c>
       <c r="K6" s="11">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="L6" s="11">
-        <v>270</v>
+        <v>15</v>
       </c>
       <c r="M6" s="11">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="N6" s="11">
         <v>0.2</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="11">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="C7" s="11">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="D7" s="11">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="E7" s="11">
         <v>4</v>
@@ -3983,27 +6996,27 @@
         <v>120</v>
       </c>
       <c r="K7" s="11">
+        <v>30</v>
+      </c>
+      <c r="L7" s="11">
         <v>270</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>150</v>
-      </c>
-      <c r="M7" s="11">
-        <v>30</v>
       </c>
       <c r="N7" s="11">
         <v>0.2</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P7" s="13" t="s">
+      <c r="P7" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="11">
         <v>220</v>
@@ -4015,13 +7028,13 @@
         <v>220</v>
       </c>
       <c r="E8" s="11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="11">
         <v>0</v>
@@ -4033,27 +7046,27 @@
         <v>120</v>
       </c>
       <c r="K8" s="11">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="L8" s="11">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M8" s="11">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="N8" s="11">
         <v>0.2</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P8" s="13" t="s">
+      <c r="P8" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" s="11">
         <v>220</v>
@@ -4065,13 +7078,13 @@
         <v>220</v>
       </c>
       <c r="E9" s="11">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F9" s="11">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G9" s="11">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="H9" s="11">
         <v>0</v>
@@ -4083,45 +7096,45 @@
         <v>120</v>
       </c>
       <c r="K9" s="11">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L9" s="11">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="M9" s="11">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="N9" s="11">
         <v>0.2</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="P9" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="11">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="C10" s="11">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="D10" s="11">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="E10" s="11">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F10" s="11">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="G10" s="11">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="H10" s="11">
         <v>0</v>
@@ -4133,45 +7146,45 @@
         <v>120</v>
       </c>
       <c r="K10" s="11">
+        <v>90</v>
+      </c>
+      <c r="L10" s="11">
         <v>330</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M10" s="11">
         <v>210</v>
-      </c>
-      <c r="M10" s="11">
-        <v>90</v>
       </c>
       <c r="N10" s="11">
         <v>0.2</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O10" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P10" s="13" t="s">
+      <c r="P10" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="11">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="C11" s="11">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="D11" s="11">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="E11" s="11">
-        <v>0.05</v>
+        <v>2.5</v>
       </c>
       <c r="F11" s="11">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="11">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H11" s="11">
         <v>0</v>
@@ -4183,27 +7196,27 @@
         <v>120</v>
       </c>
       <c r="K11" s="11">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="L11" s="11">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="M11" s="11">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N11" s="11">
         <v>0.2</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="O11" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="P11" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B12" s="11">
         <v>220</v>
@@ -4214,14 +7227,14 @@
       <c r="D12" s="11">
         <v>220</v>
       </c>
-      <c r="E12" s="14">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F12" s="14">
-        <v>0.03</v>
-      </c>
-      <c r="G12" s="14">
-        <v>4.4999999999999998E-2</v>
+      <c r="E12" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0.25</v>
       </c>
       <c r="H12" s="11">
         <v>0</v>
@@ -4241,19 +7254,19 @@
       <c r="M12" s="11">
         <v>120</v>
       </c>
-      <c r="N12" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="O12" s="13" t="s">
+      <c r="N12" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O12" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="P12" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B13" s="11">
         <v>220</v>
@@ -4264,14 +7277,14 @@
       <c r="D13" s="11">
         <v>220</v>
       </c>
-      <c r="E13" s="15">
-        <v>2E-3</v>
-      </c>
-      <c r="F13" s="15">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G13" s="15">
-        <v>4.0000000000000001E-3</v>
+      <c r="E13" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="G13" s="13">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H13" s="11">
         <v>0</v>
@@ -4291,19 +7304,19 @@
       <c r="M13" s="11">
         <v>120</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="O13" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="P13" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B14" s="11">
         <v>220</v>
@@ -4314,14 +7327,14 @@
       <c r="D14" s="11">
         <v>220</v>
       </c>
-      <c r="E14" s="15">
-        <v>0</v>
-      </c>
-      <c r="F14" s="15">
-        <v>0</v>
-      </c>
-      <c r="G14" s="15">
-        <v>0</v>
+      <c r="E14" s="14">
+        <v>2E-3</v>
+      </c>
+      <c r="F14" s="14">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H14" s="11">
         <v>0</v>
@@ -4341,37 +7354,37 @@
       <c r="M14" s="11">
         <v>120</v>
       </c>
-      <c r="N14" s="13" t="s">
+      <c r="N14" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P14" s="13" t="s">
+      <c r="P14" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15" s="14">
-        <v>68</v>
-      </c>
-      <c r="C15" s="14">
-        <v>30</v>
-      </c>
-      <c r="D15" s="14">
-        <v>10</v>
-      </c>
-      <c r="E15" s="11">
-        <v>1</v>
-      </c>
-      <c r="F15" s="11">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11">
-        <v>1</v>
+        <v>173</v>
+      </c>
+      <c r="B15" s="11">
+        <v>220</v>
+      </c>
+      <c r="C15" s="11">
+        <v>220</v>
+      </c>
+      <c r="D15" s="11">
+        <v>220</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
       </c>
       <c r="H15" s="11">
         <v>0</v>
@@ -4391,28 +7404,28 @@
       <c r="M15" s="11">
         <v>120</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="N15" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="O15" s="13" t="s">
+      <c r="O15" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P15" s="13" t="s">
+      <c r="P15" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="15">
-        <v>9</v>
-      </c>
-      <c r="C16" s="15">
-        <v>9</v>
-      </c>
-      <c r="D16" s="15">
-        <v>9</v>
+        <v>174</v>
+      </c>
+      <c r="B16" s="13">
+        <v>68</v>
+      </c>
+      <c r="C16" s="13">
+        <v>30</v>
+      </c>
+      <c r="D16" s="13">
+        <v>10</v>
       </c>
       <c r="E16" s="11">
         <v>1</v>
@@ -4441,37 +7454,37 @@
       <c r="M16" s="11">
         <v>120</v>
       </c>
-      <c r="N16" s="13" t="s">
+      <c r="N16" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="O16" s="13" t="s">
+      <c r="O16" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P16" s="13" t="s">
+      <c r="P16" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="11">
-        <v>120</v>
-      </c>
-      <c r="C17" s="11">
-        <v>120</v>
-      </c>
-      <c r="D17" s="11">
-        <v>120</v>
+        <v>175</v>
+      </c>
+      <c r="B17" s="14">
+        <v>9</v>
+      </c>
+      <c r="C17" s="14">
+        <v>9</v>
+      </c>
+      <c r="D17" s="14">
+        <v>9</v>
       </c>
       <c r="E17" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" s="11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" s="11">
         <v>0</v>
@@ -4491,37 +7504,37 @@
       <c r="M17" s="11">
         <v>120</v>
       </c>
-      <c r="N17" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="P17" s="13" t="s">
+      <c r="N17" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P17" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B18" s="11">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C18" s="11">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D18" s="11">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E18" s="11">
         <v>3</v>
       </c>
       <c r="F18" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" s="11">
         <v>0</v>
@@ -4533,45 +7546,45 @@
         <v>120</v>
       </c>
       <c r="K18" s="11">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="L18" s="11">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="M18" s="11">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N18" s="11">
         <v>0.2</v>
       </c>
-      <c r="O18" s="13" t="s">
+      <c r="O18" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="P18" s="13" t="s">
+      <c r="P18" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B19" s="11">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="C19" s="11">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="D19" s="11">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="E19" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="11">
         <v>0</v>
@@ -4583,45 +7596,45 @@
         <v>120</v>
       </c>
       <c r="K19" s="11">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="L19" s="11">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="M19" s="11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N19" s="11">
         <v>0.2</v>
       </c>
-      <c r="O19" s="13" t="s">
+      <c r="O19" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="P19" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B20" s="11">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C20" s="11">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D20" s="11">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E20" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="11">
         <v>0</v>
@@ -4633,36 +7646,36 @@
         <v>120</v>
       </c>
       <c r="K20" s="11">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="L20" s="11">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="M20" s="11">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="N20" s="11">
         <v>0.2</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="O20" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="P20" s="13" t="s">
+      <c r="P20" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B21" s="11">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="C21" s="11">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="D21" s="11">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="E21" s="11">
         <v>5</v>
@@ -4683,42 +7696,42 @@
         <v>120</v>
       </c>
       <c r="K21" s="11">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="L21" s="11">
-        <v>270</v>
+        <v>15</v>
       </c>
       <c r="M21" s="11">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="N21" s="11">
         <v>0.2</v>
       </c>
-      <c r="O21" s="13" t="s">
+      <c r="O21" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="P21" s="13" t="s">
+      <c r="P21" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>177</v>
+      <c r="A22" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="B22" s="11">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="C22" s="11">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="D22" s="11">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E22" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="11">
         <v>5</v>
@@ -4733,27 +7746,27 @@
         <v>120</v>
       </c>
       <c r="K22" s="11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L22" s="11">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="M22" s="11">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="N22" s="11">
         <v>0.2</v>
       </c>
-      <c r="O22" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>178</v>
+      <c r="O22" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>179</v>
+      <c r="A23" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="B23" s="11">
         <v>120</v>
@@ -4783,21 +7796,71 @@
         <v>120</v>
       </c>
       <c r="K23" s="11">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="M23" s="11">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N23" s="11">
         <v>0.2</v>
       </c>
-      <c r="O23" s="13" t="s">
+      <c r="O23" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="P23" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="11">
+        <v>120</v>
+      </c>
+      <c r="C24" s="11">
+        <v>120</v>
+      </c>
+      <c r="D24" s="11">
+        <v>120</v>
+      </c>
+      <c r="E24" s="11">
+        <v>3</v>
+      </c>
+      <c r="F24" s="11">
+        <v>4</v>
+      </c>
+      <c r="G24" s="11">
+        <v>5</v>
+      </c>
+      <c r="H24" s="11">
+        <v>0</v>
+      </c>
+      <c r="I24" s="11">
+        <v>240</v>
+      </c>
+      <c r="J24" s="11">
+        <v>120</v>
+      </c>
+      <c r="K24" s="11">
+        <v>330</v>
+      </c>
+      <c r="L24" s="11">
+        <v>210</v>
+      </c>
+      <c r="M24" s="11">
+        <v>90</v>
+      </c>
+      <c r="N24" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P24" s="11" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4810,7 +7873,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF2B044-25DE-40D8-A81E-5B863761CF5D}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.6640625" customWidth="1"/>
@@ -5025,26 +8088,26 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>118</v>
+      <c r="A5" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B5">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="C5">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="D5">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5056,13 +8119,13 @@
         <v>120</v>
       </c>
       <c r="K5">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="L5">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N5">
         <v>0.2</v>
@@ -5076,25 +8139,25 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B6">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C6">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D6">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5106,13 +8169,13 @@
         <v>120</v>
       </c>
       <c r="K6">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="M6">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0.2</v>
@@ -5126,25 +8189,25 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="C7">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="D7">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5156,13 +8219,13 @@
         <v>120</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="L7">
-        <v>270</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="N7">
         <v>0.2</v>
@@ -5176,25 +8239,25 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B8">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="C8">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="D8">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5206,13 +8269,13 @@
         <v>120</v>
       </c>
       <c r="K8">
+        <v>30</v>
+      </c>
+      <c r="L8">
         <v>270</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>150</v>
-      </c>
-      <c r="M8">
-        <v>30</v>
       </c>
       <c r="N8">
         <v>0.2</v>
@@ -5226,7 +8289,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>220</v>
@@ -5238,13 +8301,13 @@
         <v>220</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5256,13 +8319,13 @@
         <v>120</v>
       </c>
       <c r="K9">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="L9">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="N9">
         <v>0.2</v>
@@ -5276,7 +8339,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B10">
         <v>220</v>
@@ -5288,13 +8351,13 @@
         <v>220</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5306,13 +8369,13 @@
         <v>120</v>
       </c>
       <c r="K10">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L10">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="M10">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="N10">
         <v>0.2</v>
@@ -5326,25 +8389,25 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B11">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="C11">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="E11">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5356,13 +8419,13 @@
         <v>120</v>
       </c>
       <c r="K11">
+        <v>90</v>
+      </c>
+      <c r="L11">
         <v>330</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>210</v>
-      </c>
-      <c r="M11">
-        <v>90</v>
       </c>
       <c r="N11">
         <v>0.2</v>
@@ -5376,25 +8439,25 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B12">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="C12">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="D12">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5406,13 +8469,13 @@
         <v>120</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="L12">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N12">
         <v>0.2</v>
@@ -5426,7 +8489,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B13">
         <v>220</v>
@@ -5437,15 +8500,15 @@
       <c r="D13">
         <v>220</v>
       </c>
-      <c r="E13" s="9">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="F13" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="G13" s="9">
+      <c r="E13">
         <v>0.2</v>
       </c>
+      <c r="F13">
+        <v>0.5</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
       <c r="H13">
         <v>0</v>
       </c>
@@ -5464,8 +8527,8 @@
       <c r="M13">
         <v>120</v>
       </c>
-      <c r="N13" s="8" t="s">
-        <v>74</v>
+      <c r="N13">
+        <v>0.2</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>112</v>
@@ -5476,7 +8539,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B14">
         <v>220</v>
@@ -5487,14 +8550,14 @@
       <c r="D14">
         <v>220</v>
       </c>
-      <c r="E14" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="F14" s="10">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0.01</v>
+      <c r="E14" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0.2</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5526,7 +8589,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B15">
         <v>220</v>
@@ -5538,13 +8601,13 @@
         <v>220</v>
       </c>
       <c r="E15" s="10">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F15" s="10">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G15" s="10">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -5576,25 +8639,25 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="9">
-        <v>68</v>
-      </c>
-      <c r="C16" s="9">
-        <v>30</v>
-      </c>
-      <c r="D16" s="9">
-        <v>10</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
+        <v>135</v>
+      </c>
+      <c r="B16">
+        <v>220</v>
+      </c>
+      <c r="C16">
+        <v>220</v>
+      </c>
+      <c r="D16">
+        <v>220</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5626,16 +8689,16 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="10">
-        <v>9</v>
-      </c>
-      <c r="C17" s="10">
-        <v>9</v>
-      </c>
-      <c r="D17" s="10">
-        <v>9</v>
+        <v>136</v>
+      </c>
+      <c r="B17" s="9">
+        <v>68</v>
+      </c>
+      <c r="C17" s="9">
+        <v>30</v>
+      </c>
+      <c r="D17" s="9">
+        <v>10</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -5676,25 +8739,25 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18">
-        <v>120</v>
-      </c>
-      <c r="C18">
-        <v>120</v>
-      </c>
-      <c r="D18">
-        <v>120</v>
+        <v>137</v>
+      </c>
+      <c r="B18" s="10">
+        <v>9</v>
+      </c>
+      <c r="C18" s="10">
+        <v>9</v>
+      </c>
+      <c r="D18" s="10">
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -5706,19 +8769,19 @@
         <v>120</v>
       </c>
       <c r="K18">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="M18">
-        <v>90</v>
-      </c>
-      <c r="N18">
-        <v>0.2</v>
+        <v>120</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>74</v>
@@ -5726,25 +8789,25 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B19">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C19">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D19">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -5756,13 +8819,13 @@
         <v>120</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="L19">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N19">
         <v>0.2</v>
@@ -5776,25 +8839,25 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B20">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="C20">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="D20">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -5806,13 +8869,13 @@
         <v>120</v>
       </c>
       <c r="K20">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N20">
         <v>0.2</v>
@@ -5826,25 +8889,25 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B21">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C21">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D21">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -5856,13 +8919,13 @@
         <v>120</v>
       </c>
       <c r="K21">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="L21">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="M21">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0.2</v>
@@ -5876,25 +8939,25 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B22">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="C22">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="D22">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -5906,13 +8969,13 @@
         <v>120</v>
       </c>
       <c r="K22">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="L22">
-        <v>270</v>
+        <v>15</v>
       </c>
       <c r="M22">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="N22">
         <v>0.2</v>
@@ -5921,6 +8984,56 @@
         <v>113</v>
       </c>
       <c r="P22" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23">
+        <v>400</v>
+      </c>
+      <c r="C23">
+        <v>400</v>
+      </c>
+      <c r="D23">
+        <v>400</v>
+      </c>
+      <c r="E23">
+        <v>20</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>20</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>240</v>
+      </c>
+      <c r="J23">
+        <v>120</v>
+      </c>
+      <c r="K23">
+        <v>30</v>
+      </c>
+      <c r="L23">
+        <v>270</v>
+      </c>
+      <c r="M23">
+        <v>150</v>
+      </c>
+      <c r="N23">
+        <v>0.2</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6000,10 +9113,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E4">
         <v>0.1</v>
